--- a/docs/downloads/经营分_津河省区__津西北片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__津西北片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1115,17 +1115,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6722060729827985411</t>
+          <t>7251435992089888800</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店天津宁河贸易开发区店</t>
+          <t>维也纳酒店(5.0天津奥体中心水上公园店)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(天津宁河贸易开发区店)</t>
+          <t>维也纳酒店(5.0天津奥体中心水上公园店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1134,14 +1134,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
         <v>20</v>
@@ -1196,29 +1196,25 @@
           <t>津西北片区</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7091554083240151078</t>
+          <t>6722060729827985411</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>白玉兰（商务）天津宝坻怡购商场南环西路酒店</t>
+          <t>希岸·轻雅酒店天津宁河贸易开发区店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(天津宝坻怡购商场南环西路店)</t>
+          <t>希岸·轻雅酒店(天津宁河贸易开发区店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1239,13 +1235,13 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
@@ -1291,55 +1287,55 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7475952066058258444</t>
+          <t>7091554083240151078</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>非繁城品（天津西站熙悦汇店）</t>
+          <t>白玉兰（商务）天津宝坻怡购商场南环西路酒店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>非繁城品(天津西站熙悦汇店)</t>
+          <t>白玉兰商务酒店(天津宝坻怡购商场南环西路店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1379,17 +1375,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6843936256708102151</t>
+          <t>7475952066058258444</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>喆啡酒店天津一中心医院地铁站南开大学店</t>
+          <t>非繁城品（天津西站熙悦汇店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津一中心医院地铁站南开大学店)</t>
+          <t>非繁城品(天津西站熙悦汇店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1398,18 +1394,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>10</v>
@@ -1467,17 +1463,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6694937194131376131</t>
+          <t>6843936256708102151</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津奥体中心凌宾路地铁站店）</t>
+          <t>喆啡酒店天津一中心医院地铁站南开大学店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津奥体中心凌宾路地铁站店)</t>
+          <t>喆啡酒店(天津一中心医院地铁站南开大学店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1555,17 +1551,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6814704502403352590</t>
+          <t>6694937194131376131</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津西站人民医院地铁站店）</t>
+          <t>喆啡酒店（天津奥体中心凌宾路地铁站店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津西站人民医院地铁站店)</t>
+          <t>喆啡酒店(天津奥体中心凌宾路地铁站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1643,29 +1639,29 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6876418317968574479</t>
+          <t>6814704502403352590</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津西站天津之眼复兴路地铁站店）</t>
+          <t>喆啡酒店（天津西站人民医院地铁站店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津西站北广场卓朗科技发展店)</t>
+          <t>喆啡酒店(天津西站人民医院地铁站店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>87</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1731,22 +1727,22 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7054677357143001128</t>
+          <t>6876418317968574479</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>天津大学五大道锦江都城酒店</t>
+          <t>喆啡酒店（天津西站天津之眼复兴路地铁站店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>锦江都城(天津大学总医院五大道店)</t>
+          <t>喆啡酒店(天津西站北广场卓朗科技发展店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1773,13 +1769,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1812,20 +1808,24 @@
           <t>津西北片区</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6667085073147283469</t>
+          <t>7054677357143001128</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津西站人民医院地铁站店</t>
+          <t>天津大学五大道锦江都城酒店</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津西站人民医院地铁站店)</t>
+          <t>锦江都城(天津大学总医院五大道店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1837,7 +1837,7 @@
         <v>87</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1857,13 +1857,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1896,24 +1896,20 @@
           <t>津西北片区</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601140755148851204</t>
+          <t>6667085073147283469</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7天优品（天津鼓楼地铁站大悦城店）</t>
+          <t>麗枫酒店·天津西站人民医院地铁站店</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7天优品(天津鼓楼地铁站大悦城店)</t>
+          <t>麗枫酒店(天津西站人民医院地铁站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1922,10 +1918,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1939,7 +1935,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
@@ -1991,29 +1987,29 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6962005731608397861</t>
+          <t>6601140755148851204</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津鞍山西道地铁站店）</t>
+          <t>7天优品（天津鼓楼地铁站大悦城店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津鞍山西道地铁站店)</t>
+          <t>7天优品(天津鼓楼地铁站大悦城店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2027,7 +2023,7 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
@@ -2039,7 +2035,7 @@
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2079,17 +2075,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6856745426805147648</t>
+          <t>6962005731608397861</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津奥体中心天塔店）</t>
+          <t>喆啡酒店（天津鞍山西道地铁站店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津奥体中心天塔店)</t>
+          <t>喆啡酒店(天津鞍山西道地铁站店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2101,7 +2097,7 @@
         <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2121,13 +2117,13 @@
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2167,29 +2163,29 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7002795464235960356</t>
+          <t>6856745426805147648</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津奥体中心店</t>
+          <t>维也纳酒店（天津奥体中心天塔店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津奥体中心店)</t>
+          <t>维也纳酒店(天津奥体中心天塔店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2209,13 +2205,13 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2255,17 +2251,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6702573180134885388</t>
+          <t>7002795464235960356</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津西站湘潭道店</t>
+          <t>麗枫酒店·天津奥体中心店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津西站湘潭道店)</t>
+          <t>麗枫酒店(天津奥体中心店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2277,7 +2273,7 @@
         <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2343,17 +2339,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6601137242222118916</t>
+          <t>6702573180134885388</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>锦江之星（天津西站咸阳路地铁站店）</t>
+          <t>麗枫酒店·天津西站湘潭道店</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>锦江之星(天津长江道店)</t>
+          <t>麗枫酒店(天津西站湘潭道店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2379,7 +2375,7 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
@@ -2431,17 +2427,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7313827518157424677</t>
+          <t>6601137242222118916</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0天津宁河现代产业园民航大学店）</t>
+          <t>锦江之星（天津西站咸阳路地铁站店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津宁河现代产业园民航大学店)</t>
+          <t>锦江之星(天津长江道店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2450,14 +2446,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2467,19 +2463,19 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2519,17 +2515,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7210590186168649784</t>
+          <t>7313827518157424677</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0天津宝坻人民政府店）</t>
+          <t>维也纳酒店（5.0天津宁河现代产业园民航大学店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津宝坻民政局东城北路店)</t>
+          <t>维也纳酒店(天津宁河现代产业园民航大学店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2541,11 +2537,11 @@
         <v>97</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2561,13 +2557,13 @@
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2607,33 +2603,33 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601138014561241095</t>
+          <t>7210590186168649784</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7天酒店（天津宁河光明路店）</t>
+          <t>维也纳酒店（5.0天津宝坻人民政府店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7天酒店(天津宁河光明路店)</t>
+          <t>维也纳酒店(天津宝坻民政局东城北路店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2643,13 +2639,13 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
@@ -2695,33 +2691,33 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6601145666133559304</t>
+          <t>6601138014561241095</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IU酒店（天津南开大学一中心医院店）</t>
+          <t>7天酒店（天津宁河光明路店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IU酒店(天津南开大学一中心医院店)</t>
+          <t>7天酒店(天津宁河光明路店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2731,13 +2727,13 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
@@ -2783,29 +2779,29 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7231912388596664377</t>
+          <t>6601145666133559304</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0天津蓟州独乐寺万达广场店）</t>
+          <t>IU酒店（天津南开大学一中心医院店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳酒店 (天津蓟州渔阳南路店)</t>
+          <t>IU酒店(天津南开大学一中心医院店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2853,9 +2849,97 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>津西北片区</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>7231912388596664377</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>维也纳酒店（5.0天津蓟州独乐寺万达广场店）</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>维也纳酒店 (天津蓟州渔阳南路店)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>未认证</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>稳房源,提质量,拿收益</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" t="n">
+        <v>25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>30</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>20</v>
+      </c>
+      <c r="R27" t="n">
+        <v>30</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="n">
+        <v>20</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V26"/>
-  <conditionalFormatting sqref="H2:H26">
+  <autoFilter ref="A1:V27"/>
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2867,7 +2951,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
